--- a/public/OvertimeData/template-spkl-rev.xlsx
+++ b/public/OvertimeData/template-spkl-rev.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA943C43-03C5-41C7-BB8E-274DB3DF3BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EA8801-9BF1-43E5-A0E1-0A120A8D8225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>No</t>
   </si>
@@ -48,41 +48,46 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Lembur</t>
-  </si>
-  <si>
     <t>Masuk</t>
   </si>
   <si>
-    <t>EN-4-114</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>EN-4-104</t>
+    <t>EK-R3-010</t>
+  </si>
+  <si>
+    <t>EK-R3-054</t>
+  </si>
+  <si>
+    <t>EK-R3-057</t>
+  </si>
+  <si>
+    <t>EK-R3-055</t>
+  </si>
+  <si>
+    <t>EK-R3-065</t>
+  </si>
+  <si>
+    <t>EK-R3-068</t>
+  </si>
+  <si>
+    <t>EK-R3-026</t>
+  </si>
+  <si>
+    <t>EK-R3-070</t>
+  </si>
+  <si>
+    <t>Piket</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -153,37 +158,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{3D95199A-6F6F-4478-98E3-56A8C29C4508}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -442,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -491,19 +495,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="7">
-        <v>45890</v>
+        <v>46070</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -515,16 +519,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="7">
-        <v>45891</v>
+        <v>46070</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="6">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
       </c>
       <c r="G3" s="5"/>
     </row>
@@ -533,19 +537,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7">
-        <v>45908</v>
+        <v>46070</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
       </c>
       <c r="G4" s="5"/>
     </row>
@@ -554,19 +558,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="7">
-        <v>45920</v>
+        <v>46070</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="6">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -575,19 +579,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7">
-        <v>45890</v>
+        <v>46070</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
       </c>
       <c r="G6" s="5"/>
     </row>
@@ -596,19 +600,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7">
-        <v>45891</v>
+        <v>46070</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
       </c>
       <c r="G7" s="5"/>
     </row>
@@ -617,18 +621,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7">
-        <v>45901</v>
+        <v>46070</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6">
+        <v>7</v>
+      </c>
+      <c r="F8" s="8">
         <v>1</v>
       </c>
       <c r="G8" s="5"/>
@@ -638,210 +642,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="7">
-        <v>45907</v>
+        <v>46070</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="6">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7">
-        <v>45908</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="7">
-        <v>45909</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="6">
-        <v>2</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7">
-        <v>45911</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="6">
-        <v>4</v>
-      </c>
-      <c r="G12" s="5"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="7">
-        <v>45912</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="6">
-        <v>4</v>
-      </c>
-      <c r="G13" s="5"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7">
-        <v>45913</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="6">
-        <v>3</v>
-      </c>
-      <c r="G14" s="5"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>45914</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3">
-        <v>8</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>45915</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="6">
-        <v>2</v>
-      </c>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3">
-        <v>7</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="7">
-        <v>45918</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="6">
-        <v>2</v>
-      </c>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="7">
-        <v>45919</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="6">
-        <v>4</v>
-      </c>
-      <c r="G18" s="5"/>
+      <c r="D15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
